--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01431B73-FD5A-CA44-BEA0-55D66245BF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A5A21F-39A6-2847-A958-E840C370E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19740" yWindow="-19560" windowWidth="25680" windowHeight="16760" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Cervelo Aspero 2024" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="87">
   <si>
     <t>model</t>
   </si>
@@ -276,13 +276,34 @@
   </si>
   <si>
     <t>short offset</t>
+  </si>
+  <si>
+    <t>Size 48 - 80mm</t>
+  </si>
+  <si>
+    <t>Size 51 - 80mm</t>
+  </si>
+  <si>
+    <t>Size 54 - 90mm</t>
+  </si>
+  <si>
+    <t>Size 56 - 90mm</t>
+  </si>
+  <si>
+    <t>Size 58 - 100mm</t>
+  </si>
+  <si>
+    <t>Size 61 - 100mm</t>
+  </si>
+  <si>
+    <t>Stem sizing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -323,6 +344,11 @@
       <color rgb="FF050505"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Univers"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -344,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -353,6 +379,7 @@
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +410,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -431,7 +458,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1949,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2939,15 +2966,39 @@
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C28" s="1">
+        <v>80</v>
+      </c>
+      <c r="D28" s="1">
+        <v>80</v>
+      </c>
+      <c r="E28" s="1">
+        <v>90</v>
+      </c>
+      <c r="F28" s="1">
+        <v>90</v>
+      </c>
+      <c r="G28" s="1">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="S28"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" ht="22">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K29" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="S29"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" ht="22">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2969,9 +3020,12 @@
       <c r="H30" s="1">
         <v>45</v>
       </c>
+      <c r="K30" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="S30"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" ht="22">
       <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,9 +3047,12 @@
       <c r="H31" s="1">
         <v>45</v>
       </c>
+      <c r="K31" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="S31"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" ht="22">
       <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
@@ -3017,8 +3074,11 @@
       <c r="H32" s="1">
         <v>192</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="K32" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="22">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
@@ -3039,6 +3099,14 @@
       </c>
       <c r="H33" s="1">
         <v>200</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="22">
+      <c r="K34" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2750ED16-D12A-4447-AC2B-C955FD783CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF515910-7E83-3348-ACBE-322CFD7548E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>us</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -677,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1274,10 +1292,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C35">
         <f>((622 + 2*C29)/2*COS(C11*PI()/180) - C20)/SIN(C11*PI()/180)</f>
@@ -1306,192 +1324,216 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>65</v>
+      </c>
+      <c r="B41" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="B42" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>97</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>97</v>
+      </c>
+      <c r="B70" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>100</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B72" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF515910-7E83-3348-ACBE-322CFD7548E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEE684A-59CD-154D-B2C7-5BDC34944032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -233,13 +233,7 @@
     <t>tire_width_max_700c</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>tire_width_max_650b</t>
-  </si>
-  <si>
-    <t>47</t>
   </si>
   <si>
     <t>suspension_corrected</t>
@@ -1292,10 +1286,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35">
         <f>((622 + 2*C29)/2*COS(C11*PI()/180) - C20)/SIN(C11*PI()/180)</f>
@@ -1324,18 +1318,18 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1363,69 +1357,69 @@
       <c r="A41" t="s">
         <v>65</v>
       </c>
-      <c r="B41" t="s">
-        <v>66</v>
+      <c r="B41">
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="B42">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
         <v>63</v>
@@ -1433,108 +1427,108 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEE684A-59CD-154D-B2C7-5BDC34944032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B95F69-70B5-8C42-861E-74906A274C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://www.cervelo.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Fcervelo%2FaFxeH3fc4bHWiuqL_0L0ASBXV2C-PROFILE-Web.png%3Fauto%3Dformat%2Ccompress&amp;w=2600&amp;q=99</t>
   </si>
 </sst>
 </file>
@@ -735,6 +738,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B95F69-70B5-8C42-861E-74906A274C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A43928-828C-9449-AA79-043DD4306F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -332,9 +332,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -354,6 +351,15 @@
   </si>
   <si>
     <t>https://www.cervelo.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Fcervelo%2FaFxeH3fc4bHWiuqL_0L0ASBXV2C-PROFILE-Web.png%3Fauto%3Dformat%2Ccompress&amp;w=2600&amp;q=99</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Aliso Viejo, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -740,7 +746,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1294,10 +1300,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
         <v>100</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
       </c>
       <c r="C35">
         <f>((622 + 2*C29)/2*COS(C11*PI()/180) - C20)/SIN(C11*PI()/180)</f>
@@ -1326,18 +1332,18 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
         <v>104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1535,8 +1541,16 @@
       <c r="A72" t="s">
         <v>98</v>
       </c>
-      <c r="B72" t="s">
-        <v>99</v>
+      <c r="B72" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A43928-828C-9449-AA79-043DD4306F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE706E9F-114A-F046-9E3B-6689878AC3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -698,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1415,141 +1433,171 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>98</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>107</v>
       </c>
     </row>

--- a/data/gravel/Cervelo Aspero 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE706E9F-114A-F046-9E3B-6689878AC3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C8FB25-D55E-BE43-B030-1A387F8D2CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2060" windowWidth="24040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>model year</t>
-  </si>
-  <si>
-    <t>2024</t>
   </si>
   <si>
     <t>input date</t>
@@ -742,71 +739,71 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3">
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>370</v>
@@ -829,10 +826,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>505</v>
@@ -855,10 +852,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>71</v>
@@ -881,10 +878,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12">
         <v>577</v>
@@ -907,10 +904,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>78.5</v>
@@ -933,10 +930,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14">
         <v>83</v>
@@ -959,10 +956,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
       </c>
       <c r="C15">
         <v>512</v>
@@ -985,10 +982,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16">
         <v>74.5</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
       </c>
       <c r="C17">
         <v>681</v>
@@ -1037,10 +1034,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
       </c>
       <c r="C18">
         <v>62</v>
@@ -1063,10 +1060,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>700</v>
@@ -1089,10 +1086,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20">
         <v>52</v>
@@ -1115,10 +1112,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21">
         <v>990</v>
@@ -1141,10 +1138,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22">
         <v>425</v>
@@ -1167,22 +1164,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>80</v>
@@ -1205,17 +1202,17 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>45</v>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>45</v>
@@ -1261,7 +1258,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>150</v>
@@ -1284,7 +1281,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>160</v>
@@ -1307,21 +1304,21 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
         <v>58</v>
       </c>
-      <c r="B34" t="s">
-        <v>59</v>
-      </c>
       <c r="C34" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
       </c>
       <c r="C35">
         <f>((622 + 2*C29)/2*COS(C11*PI()/180) - C20)/SIN(C11*PI()/180)</f>
@@ -1350,44 +1347,44 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
         <v>101</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
         <v>103</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" t="s">
         <v>60</v>
-      </c>
-      <c r="B38" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
         <v>62</v>
-      </c>
-      <c r="B39" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41">
         <v>45</v>
@@ -1395,7 +1392,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42">
         <v>47</v>
@@ -1403,202 +1400,202 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
         <v>73</v>
-      </c>
-      <c r="B55" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" t="s">
         <v>95</v>
-      </c>
-      <c r="B76" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B79" t="s">
         <v>106</v>
-      </c>
-      <c r="B79" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
